--- a/leave-tracking/Leave Tracker.xlsx
+++ b/leave-tracking/Leave Tracker.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nurafianz\AppData\Local\Temp\MicrosoftEdgeDownloads\1b09c860-b946-4e94-b655-35e9c53006c6\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FD4980-D5F2-4589-93B1-F12137E2BE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="732" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="2026-01 Entries" sheetId="2" r:id="rId2"/>
@@ -14,37 +24,127 @@
     <sheet name="2026-10 Entries" sheetId="9" r:id="rId9"/>
     <sheet name="2026-12 Entries" sheetId="10" r:id="rId10"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="31">
+  <si>
+    <t>Leave Tracker Summary</t>
+  </si>
+  <si>
+    <t>Leave Type</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Allocated</t>
+  </si>
+  <si>
+    <t>Not set</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-12-07</t>
+  </si>
+  <si>
+    <t>2026-12-08</t>
+  </si>
+  <si>
+    <t>2026-12-09</t>
+  </si>
+  <si>
+    <t>2026-12-10</t>
+  </si>
+  <si>
+    <t>2026-12-11</t>
+  </si>
+  <si>
+    <t>2026-12-14</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -73,14 +173,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -405,485 +514,530 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Leave Tracker Summary</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Leave Type</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AL</v>
-      </c>
-      <c r="C2" t="str">
-        <v>OIL</v>
-      </c>
-      <c r="D2" t="str">
-        <v>MC</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Allocated</v>
+    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
-      <c r="C3" t="str">
-        <v>Not set</v>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
       <c r="D3">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError sqref="A1:D3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-12-07</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-12-08</v>
-      </c>
-      <c r="B3" t="str">
-        <v>AL</v>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-12-09</v>
-      </c>
-      <c r="B4" t="str">
-        <v>AL</v>
+    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-12-10</v>
-      </c>
-      <c r="B5" t="str">
-        <v>AL</v>
+    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-12-11</v>
-      </c>
-      <c r="B6" t="str">
-        <v>AL</v>
+    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026-12-14</v>
-      </c>
-      <c r="B7" t="str">
-        <v>AL</v>
+    <row r="7" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError sqref="A1:C7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-01-19</v>
-      </c>
-      <c r="B3" t="str">
-        <v>AL</v>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="B4" t="str">
-        <v>AL</v>
+    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
       <c r="C4">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError sqref="A1:C4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="B2" t="str">
-        <v>MC</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="B3" t="str">
-        <v>AL</v>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="B4" t="str">
-        <v>AL</v>
+    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="B5" t="str">
-        <v>MC</v>
+    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError sqref="A1:C5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>MC</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="B3" t="str">
-        <v>AL</v>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError sqref="A1:C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B2" t="str">
-        <v>OIL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="B3" t="str">
-        <v>AL</v>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError sqref="A1:C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="B2" t="str">
-        <v>OIL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-06-26</v>
-      </c>
-      <c r="B3" t="str">
-        <v>AL</v>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError sqref="A1:C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-07-17</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Duration</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-10-02</v>
-      </c>
-      <c r="B2" t="str">
-        <v>AL</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0.5</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError sqref="A1:C1 B2:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>